--- a/backend/data/financials_by_company/0362.HK.xlsx
+++ b/backend/data/financials_by_company/0362.HK.xlsx
@@ -682,161 +682,161 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>-2326000</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D2" t="n">
-        <v>-69017000</v>
+        <v>-149893000</v>
       </c>
       <c r="E2" t="n">
-        <v>29817000</v>
+        <v>-9304000</v>
       </c>
       <c r="F2" t="n">
-        <v>29817000</v>
+        <v>-9304000</v>
       </c>
       <c r="G2" t="n">
-        <v>-162501000</v>
+        <v>-358502000</v>
       </c>
       <c r="H2" t="n">
-        <v>38531000</v>
+        <v>81618000</v>
       </c>
       <c r="I2" t="n">
-        <v>20415000</v>
+        <v>179127000</v>
       </c>
       <c r="J2" t="n">
-        <v>-39200000</v>
+        <v>-159197000</v>
       </c>
       <c r="K2" t="n">
-        <v>-77731000</v>
+        <v>-240815000</v>
       </c>
       <c r="L2" t="n">
-        <v>-92486000</v>
+        <v>-125079000</v>
       </c>
       <c r="M2" t="n">
-        <v>92488000</v>
+        <v>126030000</v>
       </c>
       <c r="N2" t="n">
-        <v>2000</v>
+        <v>951000</v>
       </c>
       <c r="O2" t="n">
-        <v>-192318000</v>
+        <v>-351524000</v>
       </c>
       <c r="P2" t="n">
-        <v>-162501000</v>
+        <v>-450353000</v>
       </c>
       <c r="Q2" t="n">
-        <v>139351000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1281000</v>
-      </c>
+        <v>465440000</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>-77731000</v>
+        <v>-240815000</v>
       </c>
       <c r="T2" t="n">
-        <v>18001475</v>
+        <v>73370226</v>
       </c>
       <c r="U2" t="n">
-        <v>18001475</v>
+        <v>1834255</v>
       </c>
       <c r="V2" t="n">
-        <v>-9.028</v>
+        <v>-245.503911</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.2257</v>
+        <v>-6.137598</v>
       </c>
       <c r="X2" t="n">
-        <v>-162501000</v>
+        <v>-450353000</v>
       </c>
       <c r="Y2" t="n">
-        <v>-162501000</v>
+        <v>-450353000</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-162501000</v>
+        <v>-450353000</v>
       </c>
       <c r="AB2" t="n">
-        <v>7718000</v>
+        <v>9233000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-170219000</v>
+        <v>-459586000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>-91851000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-170219000</v>
+        <v>-367735000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>890000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-170219000</v>
+        <v>-366845000</v>
       </c>
       <c r="AH2" t="n">
-        <v>239000</v>
+        <v>3691000</v>
       </c>
       <c r="AI2" t="n">
-        <v>31588000</v>
+        <v>-6316000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-96599000</v>
-      </c>
-      <c r="AK2" t="inlineStr"/>
+        <v>4394000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1522000</v>
+      </c>
       <c r="AL2" t="n">
-        <v>65011000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
+        <v>1922000</v>
+      </c>
+      <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="n">
-        <v>-92486000</v>
+        <v>-125079000</v>
       </c>
       <c r="AO2" t="n">
-        <v>92488000</v>
+        <v>126030000</v>
       </c>
       <c r="AP2" t="n">
-        <v>2000</v>
+        <v>951000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-107789000</v>
+        <v>-236419000</v>
       </c>
       <c r="AR2" t="n">
-        <v>118936000</v>
+        <v>286313000</v>
       </c>
       <c r="AS2" t="n">
-        <v>24616000</v>
+        <v>155837000</v>
       </c>
       <c r="AT2" t="n">
-        <v>94320000</v>
-      </c>
-      <c r="AU2" t="inlineStr"/>
+        <v>133550000</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>27117000</v>
+      </c>
       <c r="AV2" t="n">
-        <v>94320000</v>
+        <v>106433000</v>
       </c>
       <c r="AW2" t="n">
-        <v>11147000</v>
+        <v>49894000</v>
       </c>
       <c r="AX2" t="n">
-        <v>20415000</v>
+        <v>179127000</v>
       </c>
       <c r="AY2" t="n">
-        <v>31562000</v>
+        <v>229021000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>31562000</v>
+        <v>229021000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
@@ -845,154 +845,156 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-68798000</v>
+        <v>-59308000</v>
       </c>
       <c r="E3" t="n">
-        <v>59531000</v>
+        <v>46771000</v>
       </c>
       <c r="F3" t="n">
-        <v>59531000</v>
+        <v>46771000</v>
       </c>
       <c r="G3" t="n">
-        <v>-147167000</v>
+        <v>-251382000</v>
       </c>
       <c r="H3" t="n">
-        <v>63340000</v>
+        <v>82430000</v>
       </c>
       <c r="I3" t="n">
-        <v>105947000</v>
+        <v>166181000</v>
       </c>
       <c r="J3" t="n">
-        <v>-9267000</v>
+        <v>-12537000</v>
       </c>
       <c r="K3" t="n">
-        <v>-72607000</v>
+        <v>-94967000</v>
       </c>
       <c r="L3" t="n">
-        <v>-113922000</v>
+        <v>-165997000</v>
       </c>
       <c r="M3" t="n">
-        <v>113926000</v>
+        <v>166030000</v>
       </c>
       <c r="N3" t="n">
-        <v>4000</v>
+        <v>33000</v>
       </c>
       <c r="O3" t="n">
-        <v>-206698000</v>
+        <v>-298153000</v>
       </c>
       <c r="P3" t="n">
-        <v>-155876000</v>
+        <v>-1064206000</v>
       </c>
       <c r="Q3" t="n">
-        <v>233152000</v>
+        <v>340811000</v>
       </c>
       <c r="R3" t="n">
-        <v>1097000</v>
+        <v>320000</v>
       </c>
       <c r="S3" t="n">
-        <v>-72607000</v>
+        <v>-94967000</v>
       </c>
       <c r="T3" t="n">
-        <v>318290000</v>
+        <v>111140000</v>
       </c>
       <c r="U3" t="n">
-        <v>318290000</v>
+        <v>111140000</v>
       </c>
       <c r="V3" t="n">
-        <v>-19.588</v>
+        <v>-383.016</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.4897</v>
+        <v>-9.5754</v>
       </c>
       <c r="X3" t="n">
-        <v>-155876000</v>
+        <v>-1064206000</v>
       </c>
       <c r="Y3" t="n">
-        <v>-155876000</v>
+        <v>-1064206000</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>-155876000</v>
+        <v>-1064206000</v>
       </c>
       <c r="AB3" t="n">
-        <v>39366000</v>
+        <v>9615000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-195242000</v>
+        <v>-1073821000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-8709000</v>
+        <v>-812824000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-186533000</v>
+        <v>-260997000</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>-186533000</v>
+        <v>-260997000</v>
       </c>
       <c r="AH3" t="n">
-        <v>163000</v>
+        <v>513000</v>
       </c>
       <c r="AI3" t="n">
-        <v>59380000</v>
+        <v>44815000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-416180000</v>
+        <v>-49186000</v>
       </c>
       <c r="AK3" t="n">
-        <v>3563000</v>
+        <v>-3726000</v>
       </c>
       <c r="AL3" t="n">
-        <v>359411000</v>
+        <v>4371000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-2611000</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>-113922000</v>
+        <v>-165997000</v>
       </c>
       <c r="AO3" t="n">
-        <v>113926000</v>
+        <v>166030000</v>
       </c>
       <c r="AP3" t="n">
-        <v>4000</v>
+        <v>33000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-132305000</v>
+        <v>-142147000</v>
       </c>
       <c r="AR3" t="n">
-        <v>127205000</v>
+        <v>174630000</v>
       </c>
       <c r="AS3" t="n">
-        <v>31710000</v>
+        <v>62509000</v>
       </c>
       <c r="AT3" t="n">
-        <v>95559000</v>
-      </c>
-      <c r="AU3" t="inlineStr"/>
+        <v>112233000</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>19876000</v>
+      </c>
       <c r="AV3" t="n">
-        <v>95559000</v>
+        <v>112233000</v>
       </c>
       <c r="AW3" t="n">
-        <v>-5100000</v>
+        <v>32483000</v>
       </c>
       <c r="AX3" t="n">
-        <v>105947000</v>
+        <v>166181000</v>
       </c>
       <c r="AY3" t="n">
-        <v>100847000</v>
+        <v>198664000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>100847000</v>
+        <v>198664000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
         <v>0</v>
@@ -1001,305 +1003,303 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-59308000</v>
+        <v>-68798000</v>
       </c>
       <c r="E4" t="n">
-        <v>46771000</v>
+        <v>59531000</v>
       </c>
       <c r="F4" t="n">
-        <v>46771000</v>
+        <v>59531000</v>
       </c>
       <c r="G4" t="n">
-        <v>-251382000</v>
+        <v>-147167000</v>
       </c>
       <c r="H4" t="n">
-        <v>82430000</v>
+        <v>63340000</v>
       </c>
       <c r="I4" t="n">
-        <v>166181000</v>
+        <v>105947000</v>
       </c>
       <c r="J4" t="n">
-        <v>-12537000</v>
+        <v>-9267000</v>
       </c>
       <c r="K4" t="n">
-        <v>-94967000</v>
+        <v>-72607000</v>
       </c>
       <c r="L4" t="n">
-        <v>-165997000</v>
+        <v>-113922000</v>
       </c>
       <c r="M4" t="n">
-        <v>166030000</v>
+        <v>113926000</v>
       </c>
       <c r="N4" t="n">
-        <v>33000</v>
+        <v>4000</v>
       </c>
       <c r="O4" t="n">
-        <v>-298153000</v>
+        <v>-206698000</v>
       </c>
       <c r="P4" t="n">
-        <v>-1064206000</v>
+        <v>-155876000</v>
       </c>
       <c r="Q4" t="n">
-        <v>340811000</v>
+        <v>233152000</v>
       </c>
       <c r="R4" t="n">
-        <v>320000</v>
+        <v>1097000</v>
       </c>
       <c r="S4" t="n">
-        <v>-94967000</v>
+        <v>-72607000</v>
       </c>
       <c r="T4" t="n">
-        <v>111140000</v>
+        <v>318290000</v>
       </c>
       <c r="U4" t="n">
-        <v>111140000</v>
+        <v>318290000</v>
       </c>
       <c r="V4" t="n">
-        <v>-383.016</v>
+        <v>-19.588</v>
       </c>
       <c r="W4" t="n">
-        <v>-9.5754</v>
+        <v>-0.4897</v>
       </c>
       <c r="X4" t="n">
-        <v>-1064206000</v>
+        <v>-155876000</v>
       </c>
       <c r="Y4" t="n">
-        <v>-1064206000</v>
+        <v>-155876000</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>-1064206000</v>
+        <v>-155876000</v>
       </c>
       <c r="AB4" t="n">
-        <v>9615000</v>
+        <v>39366000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1073821000</v>
+        <v>-195242000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-812824000</v>
+        <v>-8709000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-260997000</v>
+        <v>-186533000</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>-260997000</v>
+        <v>-186533000</v>
       </c>
       <c r="AH4" t="n">
-        <v>513000</v>
+        <v>163000</v>
       </c>
       <c r="AI4" t="n">
-        <v>44815000</v>
+        <v>59380000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-49186000</v>
+        <v>-416180000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-3726000</v>
+        <v>3563000</v>
       </c>
       <c r="AL4" t="n">
-        <v>4371000</v>
+        <v>359411000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>-2611000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-165997000</v>
+        <v>-113922000</v>
       </c>
       <c r="AO4" t="n">
-        <v>166030000</v>
+        <v>113926000</v>
       </c>
       <c r="AP4" t="n">
-        <v>33000</v>
+        <v>4000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-142147000</v>
+        <v>-132305000</v>
       </c>
       <c r="AR4" t="n">
-        <v>174630000</v>
+        <v>127205000</v>
       </c>
       <c r="AS4" t="n">
-        <v>62509000</v>
+        <v>31710000</v>
       </c>
       <c r="AT4" t="n">
-        <v>112233000</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>19876000</v>
-      </c>
+        <v>95559000</v>
+      </c>
+      <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="n">
-        <v>112233000</v>
+        <v>95559000</v>
       </c>
       <c r="AW4" t="n">
-        <v>32483000</v>
+        <v>-5100000</v>
       </c>
       <c r="AX4" t="n">
-        <v>166181000</v>
+        <v>105947000</v>
       </c>
       <c r="AY4" t="n">
-        <v>198664000</v>
+        <v>100847000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>198664000</v>
+        <v>100847000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>-2326000</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-149893000</v>
+        <v>-69017000</v>
       </c>
       <c r="E5" t="n">
-        <v>-9304000</v>
+        <v>29817000</v>
       </c>
       <c r="F5" t="n">
-        <v>-9304000</v>
+        <v>29817000</v>
       </c>
       <c r="G5" t="n">
-        <v>-358502000</v>
+        <v>-162501000</v>
       </c>
       <c r="H5" t="n">
-        <v>81618000</v>
+        <v>38531000</v>
       </c>
       <c r="I5" t="n">
-        <v>179127000</v>
+        <v>20415000</v>
       </c>
       <c r="J5" t="n">
-        <v>-159197000</v>
+        <v>-39200000</v>
       </c>
       <c r="K5" t="n">
-        <v>-240815000</v>
+        <v>-77731000</v>
       </c>
       <c r="L5" t="n">
-        <v>-125079000</v>
+        <v>-92486000</v>
       </c>
       <c r="M5" t="n">
-        <v>126030000</v>
+        <v>92488000</v>
       </c>
       <c r="N5" t="n">
-        <v>951000</v>
+        <v>2000</v>
       </c>
       <c r="O5" t="n">
-        <v>-351524000</v>
+        <v>-192318000</v>
       </c>
       <c r="P5" t="n">
-        <v>-450353000</v>
+        <v>-162501000</v>
       </c>
       <c r="Q5" t="n">
-        <v>465440000</v>
-      </c>
-      <c r="R5" t="inlineStr"/>
+        <v>139351000</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1281000</v>
+      </c>
       <c r="S5" t="n">
-        <v>-240815000</v>
+        <v>-77731000</v>
       </c>
       <c r="T5" t="n">
-        <v>73370226</v>
+        <v>18001475</v>
       </c>
       <c r="U5" t="n">
-        <v>1834255</v>
+        <v>18001475</v>
       </c>
       <c r="V5" t="n">
-        <v>-245.503911</v>
+        <v>-9.028</v>
       </c>
       <c r="W5" t="n">
-        <v>-6.137598</v>
+        <v>-0.2257</v>
       </c>
       <c r="X5" t="n">
-        <v>-450353000</v>
+        <v>-162501000</v>
       </c>
       <c r="Y5" t="n">
-        <v>-450353000</v>
+        <v>-162501000</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>-450353000</v>
+        <v>-162501000</v>
       </c>
       <c r="AB5" t="n">
-        <v>9233000</v>
+        <v>7718000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-459586000</v>
+        <v>-170219000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-91851000</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-367735000</v>
+        <v>-170219000</v>
       </c>
       <c r="AF5" t="n">
-        <v>890000</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>-366845000</v>
+        <v>-170219000</v>
       </c>
       <c r="AH5" t="n">
-        <v>3691000</v>
+        <v>239000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-6316000</v>
+        <v>31588000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>4394000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1522000</v>
-      </c>
+        <v>-96599000</v>
+      </c>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>1922000</v>
-      </c>
-      <c r="AM5" t="inlineStr"/>
+        <v>65011000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
       <c r="AN5" t="n">
-        <v>-125079000</v>
+        <v>-92486000</v>
       </c>
       <c r="AO5" t="n">
-        <v>126030000</v>
+        <v>92488000</v>
       </c>
       <c r="AP5" t="n">
-        <v>951000</v>
+        <v>2000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-236419000</v>
+        <v>-107789000</v>
       </c>
       <c r="AR5" t="n">
-        <v>286313000</v>
+        <v>118936000</v>
       </c>
       <c r="AS5" t="n">
-        <v>155837000</v>
+        <v>24616000</v>
       </c>
       <c r="AT5" t="n">
-        <v>133550000</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>27117000</v>
-      </c>
+        <v>94320000</v>
+      </c>
+      <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="n">
-        <v>106433000</v>
+        <v>94320000</v>
       </c>
       <c r="AW5" t="n">
-        <v>49894000</v>
+        <v>11147000</v>
       </c>
       <c r="AX5" t="n">
-        <v>179127000</v>
+        <v>20415000</v>
       </c>
       <c r="AY5" t="n">
-        <v>229021000</v>
+        <v>31562000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>229021000</v>
+        <v>31562000</v>
       </c>
     </row>
   </sheetData>
@@ -1655,121 +1655,119 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
-      </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
+        <v>44377</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>33788704</v>
+        <v>2047225</v>
       </c>
       <c r="D2" t="n">
-        <v>33788704</v>
+        <v>2047225</v>
       </c>
       <c r="E2" t="n">
-        <v>1137761000</v>
+        <v>1212190000</v>
       </c>
       <c r="F2" t="n">
-        <v>1170801000</v>
+        <v>1262723000</v>
       </c>
       <c r="G2" t="n">
-        <v>-1008984000</v>
+        <v>29564000</v>
       </c>
       <c r="H2" t="n">
-        <v>159482000</v>
+        <v>1288529000</v>
       </c>
       <c r="I2" t="n">
-        <v>-1004115000</v>
+        <v>-958412000</v>
       </c>
       <c r="J2" t="n">
-        <v>-1008984000</v>
+        <v>29564000</v>
       </c>
       <c r="K2" t="n">
-        <v>2335000</v>
+        <v>3758000</v>
       </c>
       <c r="L2" t="n">
-        <v>-1008984000</v>
+        <v>29564000</v>
       </c>
       <c r="M2" t="n">
-        <v>-576888000</v>
+        <v>726780000</v>
       </c>
       <c r="N2" t="n">
-        <v>-1009144000</v>
+        <v>88709000</v>
       </c>
       <c r="O2" t="n">
-        <v>-160000</v>
+        <v>59145000</v>
       </c>
       <c r="P2" t="n">
-        <v>-1008984000</v>
+        <v>29564000</v>
       </c>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="n">
-        <v>-1757869000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>513550000</v>
-      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
-        <v>135155000</v>
+        <v>160371000</v>
       </c>
       <c r="U2" t="n">
-        <v>135155000</v>
+        <v>160371000</v>
       </c>
       <c r="V2" t="n">
-        <v>1487244000</v>
+        <v>1982644000</v>
       </c>
       <c r="W2" t="n">
-        <v>432897000</v>
+        <v>698699000</v>
       </c>
       <c r="X2" t="n">
-        <v>432897000</v>
+        <v>698699000</v>
       </c>
       <c r="Y2" t="n">
-        <v>801000</v>
+        <v>1483000</v>
       </c>
       <c r="Z2" t="n">
-        <v>432096000</v>
+        <v>697216000</v>
       </c>
       <c r="AA2" t="n">
-        <v>1054347000</v>
+        <v>1283945000</v>
       </c>
       <c r="AB2" t="n">
-        <v>737904000</v>
+        <v>564024000</v>
       </c>
       <c r="AC2" t="n">
-        <v>1534000</v>
+        <v>2275000</v>
       </c>
       <c r="AD2" t="n">
-        <v>736370000</v>
+        <v>561749000</v>
       </c>
       <c r="AE2" t="n">
-        <v>24686000</v>
+        <v>71082000</v>
       </c>
       <c r="AF2" t="n">
-        <v>276230000</v>
+        <v>570758000</v>
       </c>
       <c r="AG2" t="n">
-        <v>233686000</v>
-      </c>
-      <c r="AH2" t="inlineStr"/>
+        <v>517803000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>878000</v>
+      </c>
       <c r="AI2" t="n">
-        <v>42544000</v>
+        <v>52077000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>478100000</v>
+        <v>2071353000</v>
       </c>
       <c r="AK2" t="n">
-        <v>427868000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>342000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>342000</v>
-      </c>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
+        <v>1745820000</v>
+      </c>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="n">
+        <v>10108000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>10108000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>10108000</v>
+      </c>
       <c r="AQ2" t="n">
         <v>0</v>
       </c>
@@ -1777,191 +1775,187 @@
         <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>427526000</v>
+        <v>1735712000</v>
       </c>
       <c r="AT2" t="n">
-        <v>-1107687000</v>
+        <v>-902045000</v>
       </c>
       <c r="AU2" t="n">
-        <v>1535213000</v>
+        <v>2637757000</v>
       </c>
       <c r="AV2" t="n">
-        <v>9102000</v>
-      </c>
-      <c r="AW2" t="inlineStr"/>
+        <v>487965000</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>162393000</v>
+      </c>
       <c r="AX2" t="n">
-        <v>935693000</v>
+        <v>1120552000</v>
       </c>
       <c r="AY2" t="n">
-        <v>393007000</v>
+        <v>590093000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>197411000</v>
+        <v>276754000</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>50232000</v>
+        <v>325533000</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>112343000</v>
       </c>
       <c r="BD2" t="n">
-        <v>4249000</v>
+        <v>45288000</v>
       </c>
       <c r="BE2" t="n">
-        <v>10672000</v>
+        <v>5735000</v>
       </c>
       <c r="BF2" t="n">
-        <v>-1218000</v>
+        <v>-3704000</v>
       </c>
       <c r="BG2" t="n">
-        <v>7180000</v>
+        <v>1112000</v>
       </c>
       <c r="BH2" t="n">
-        <v>4710000</v>
+        <v>8327000</v>
       </c>
       <c r="BI2" t="n">
-        <v>3704000</v>
+        <v>91808000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>848000</v>
+        <v>23020000</v>
       </c>
       <c r="BK2" t="n">
-        <v>-7224000</v>
+        <v>-19353000</v>
       </c>
       <c r="BL2" t="n">
-        <v>8072000</v>
+        <v>42373000</v>
       </c>
       <c r="BM2" t="n">
-        <v>30759000</v>
+        <v>47339000</v>
       </c>
       <c r="BN2" t="n">
-        <v>54000</v>
+        <v>564000</v>
       </c>
       <c r="BO2" t="n">
-        <v>30705000</v>
+        <v>46775000</v>
       </c>
       <c r="BP2" t="n">
-        <v>30705000</v>
+        <v>46775000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>13188704</v>
+        <v>3396360</v>
       </c>
       <c r="D3" t="n">
-        <v>13188704</v>
+        <v>135854423</v>
       </c>
       <c r="E3" t="n">
-        <v>1171484000</v>
+        <v>1242539000</v>
       </c>
       <c r="F3" t="n">
-        <v>1174382000</v>
+        <v>1256896000</v>
       </c>
       <c r="G3" t="n">
-        <v>-955357000</v>
+        <v>-873168000</v>
       </c>
       <c r="H3" t="n">
-        <v>219025000</v>
+        <v>382245000</v>
       </c>
       <c r="I3" t="n">
-        <v>-794788000</v>
+        <v>-966539000</v>
       </c>
       <c r="J3" t="n">
-        <v>-955357000</v>
+        <v>-873168000</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1483000</v>
       </c>
       <c r="L3" t="n">
-        <v>-955357000</v>
+        <v>-873168000</v>
       </c>
       <c r="M3" t="n">
-        <v>-181491000</v>
+        <v>73407000</v>
       </c>
       <c r="N3" t="n">
-        <v>-947719000</v>
+        <v>-824850000</v>
       </c>
       <c r="O3" t="n">
-        <v>7638000</v>
+        <v>48318000</v>
       </c>
       <c r="P3" t="n">
-        <v>-955357000</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>28519000</v>
-      </c>
-      <c r="R3" t="n">
-        <v>-1617769000</v>
-      </c>
-      <c r="S3" t="n">
-        <v>496071000</v>
-      </c>
+        <v>-873168000</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
-        <v>52755000</v>
+        <v>266056000</v>
       </c>
       <c r="U3" t="n">
-        <v>52755000</v>
+        <v>266056000</v>
       </c>
       <c r="V3" t="n">
-        <v>1614348000</v>
+        <v>2063097000</v>
       </c>
       <c r="W3" t="n">
-        <v>773866000</v>
+        <v>946575000</v>
       </c>
       <c r="X3" t="n">
-        <v>773866000</v>
+        <v>946575000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>773866000</v>
+        <v>946575000</v>
       </c>
       <c r="AA3" t="n">
-        <v>840482000</v>
+        <v>1116522000</v>
       </c>
       <c r="AB3" t="n">
-        <v>400516000</v>
+        <v>310321000</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1483000</v>
       </c>
       <c r="AD3" t="n">
-        <v>400516000</v>
+        <v>308838000</v>
       </c>
       <c r="AE3" t="n">
-        <v>8567000</v>
+        <v>76591000</v>
       </c>
       <c r="AF3" t="n">
-        <v>421037000</v>
+        <v>655352000</v>
       </c>
       <c r="AG3" t="n">
-        <v>381082000</v>
+        <v>596899000</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>815000</v>
       </c>
       <c r="AI3" t="n">
-        <v>39955000</v>
+        <v>57638000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>666629000</v>
+        <v>1238247000</v>
       </c>
       <c r="AK3" t="n">
-        <v>620935000</v>
+        <v>1088264000</v>
       </c>
       <c r="AL3" t="n">
-        <v>2075000</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>2075000</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
         <v>0</v>
@@ -1977,187 +1971,193 @@
         <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>618860000</v>
+        <v>1088264000</v>
       </c>
       <c r="AT3" t="n">
-        <v>-1074763000</v>
+        <v>-1616439000</v>
       </c>
       <c r="AU3" t="n">
-        <v>1693623000</v>
+        <v>2704703000</v>
       </c>
       <c r="AV3" t="n">
-        <v>6833000</v>
+        <v>478366000</v>
       </c>
       <c r="AW3" t="n">
-        <v>618860000</v>
+        <v>192904000</v>
       </c>
       <c r="AX3" t="n">
-        <v>951491000</v>
+        <v>1096385000</v>
       </c>
       <c r="AY3" t="n">
-        <v>506413000</v>
+        <v>690517000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>228886000</v>
+        <v>246531000</v>
       </c>
       <c r="BA3" t="n">
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>45694000</v>
+        <v>149983000</v>
       </c>
       <c r="BC3" t="n">
-        <v>8765000</v>
+        <v>9379000</v>
       </c>
       <c r="BD3" t="n">
-        <v>16182000</v>
+        <v>31157000</v>
       </c>
       <c r="BE3" t="n">
-        <v>2125000</v>
+        <v>22197000</v>
       </c>
       <c r="BF3" t="n">
-        <v>-3460000</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
-        <v>316000</v>
+        <v>16802000</v>
       </c>
       <c r="BH3" t="n">
-        <v>5269000</v>
+        <v>5395000</v>
       </c>
       <c r="BI3" t="n">
-        <v>10178000</v>
+        <v>42646000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>5430000</v>
+        <v>29759000</v>
       </c>
       <c r="BK3" t="n">
-        <v>-7000</v>
+        <v>-21719000</v>
       </c>
       <c r="BL3" t="n">
-        <v>5437000</v>
+        <v>51478000</v>
       </c>
       <c r="BM3" t="n">
-        <v>3014000</v>
+        <v>14845000</v>
       </c>
       <c r="BN3" t="n">
-        <v>116000</v>
+        <v>1971000</v>
       </c>
       <c r="BO3" t="n">
-        <v>2898000</v>
+        <v>12874000</v>
       </c>
       <c r="BP3" t="n">
-        <v>2898000</v>
+        <v>12874000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>3396360</v>
+        <v>13188704</v>
       </c>
       <c r="D4" t="n">
-        <v>135854423</v>
+        <v>13188704</v>
       </c>
       <c r="E4" t="n">
-        <v>1242539000</v>
+        <v>1171484000</v>
       </c>
       <c r="F4" t="n">
-        <v>1256896000</v>
+        <v>1174382000</v>
       </c>
       <c r="G4" t="n">
-        <v>-873168000</v>
+        <v>-955357000</v>
       </c>
       <c r="H4" t="n">
-        <v>382245000</v>
+        <v>219025000</v>
       </c>
       <c r="I4" t="n">
-        <v>-966539000</v>
+        <v>-794788000</v>
       </c>
       <c r="J4" t="n">
-        <v>-873168000</v>
+        <v>-955357000</v>
       </c>
       <c r="K4" t="n">
-        <v>1483000</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-873168000</v>
+        <v>-955357000</v>
       </c>
       <c r="M4" t="n">
-        <v>73407000</v>
+        <v>-181491000</v>
       </c>
       <c r="N4" t="n">
-        <v>-824850000</v>
+        <v>-947719000</v>
       </c>
       <c r="O4" t="n">
-        <v>48318000</v>
+        <v>7638000</v>
       </c>
       <c r="P4" t="n">
-        <v>-873168000</v>
-      </c>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
+        <v>-955357000</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>28519000</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-1617769000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>496071000</v>
+      </c>
       <c r="T4" t="n">
-        <v>266056000</v>
+        <v>52755000</v>
       </c>
       <c r="U4" t="n">
-        <v>266056000</v>
+        <v>52755000</v>
       </c>
       <c r="V4" t="n">
-        <v>2063097000</v>
+        <v>1614348000</v>
       </c>
       <c r="W4" t="n">
-        <v>946575000</v>
+        <v>773866000</v>
       </c>
       <c r="X4" t="n">
-        <v>946575000</v>
+        <v>773866000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>946575000</v>
+        <v>773866000</v>
       </c>
       <c r="AA4" t="n">
-        <v>1116522000</v>
+        <v>840482000</v>
       </c>
       <c r="AB4" t="n">
-        <v>310321000</v>
+        <v>400516000</v>
       </c>
       <c r="AC4" t="n">
-        <v>1483000</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>308838000</v>
+        <v>400516000</v>
       </c>
       <c r="AE4" t="n">
-        <v>76591000</v>
+        <v>8567000</v>
       </c>
       <c r="AF4" t="n">
-        <v>655352000</v>
+        <v>421037000</v>
       </c>
       <c r="AG4" t="n">
-        <v>596899000</v>
+        <v>381082000</v>
       </c>
       <c r="AH4" t="n">
-        <v>815000</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>57638000</v>
+        <v>39955000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1238247000</v>
+        <v>666629000</v>
       </c>
       <c r="AK4" t="n">
-        <v>1088264000</v>
+        <v>620935000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>2075000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>2075000</v>
       </c>
       <c r="AN4" t="n">
         <v>0</v>
@@ -2173,193 +2173,195 @@
         <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>1088264000</v>
+        <v>618860000</v>
       </c>
       <c r="AT4" t="n">
-        <v>-1616439000</v>
+        <v>-1074763000</v>
       </c>
       <c r="AU4" t="n">
-        <v>2704703000</v>
+        <v>1693623000</v>
       </c>
       <c r="AV4" t="n">
-        <v>478366000</v>
+        <v>6833000</v>
       </c>
       <c r="AW4" t="n">
-        <v>192904000</v>
+        <v>618860000</v>
       </c>
       <c r="AX4" t="n">
-        <v>1096385000</v>
+        <v>951491000</v>
       </c>
       <c r="AY4" t="n">
-        <v>690517000</v>
+        <v>506413000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>246531000</v>
+        <v>228886000</v>
       </c>
       <c r="BA4" t="n">
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>149983000</v>
+        <v>45694000</v>
       </c>
       <c r="BC4" t="n">
-        <v>9379000</v>
+        <v>8765000</v>
       </c>
       <c r="BD4" t="n">
-        <v>31157000</v>
+        <v>16182000</v>
       </c>
       <c r="BE4" t="n">
-        <v>22197000</v>
+        <v>2125000</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>-3460000</v>
       </c>
       <c r="BG4" t="n">
-        <v>16802000</v>
+        <v>316000</v>
       </c>
       <c r="BH4" t="n">
-        <v>5395000</v>
+        <v>5269000</v>
       </c>
       <c r="BI4" t="n">
-        <v>42646000</v>
+        <v>10178000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>29759000</v>
+        <v>5430000</v>
       </c>
       <c r="BK4" t="n">
-        <v>-21719000</v>
+        <v>-7000</v>
       </c>
       <c r="BL4" t="n">
-        <v>51478000</v>
+        <v>5437000</v>
       </c>
       <c r="BM4" t="n">
-        <v>14845000</v>
+        <v>3014000</v>
       </c>
       <c r="BN4" t="n">
-        <v>1971000</v>
+        <v>116000</v>
       </c>
       <c r="BO4" t="n">
-        <v>12874000</v>
+        <v>2898000</v>
       </c>
       <c r="BP4" t="n">
-        <v>12874000</v>
+        <v>2898000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
-      </c>
-      <c r="B5" t="inlineStr"/>
+        <v>45473</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
       <c r="C5" t="n">
-        <v>2047225</v>
+        <v>33788704</v>
       </c>
       <c r="D5" t="n">
-        <v>2047225</v>
+        <v>33788704</v>
       </c>
       <c r="E5" t="n">
-        <v>1212190000</v>
+        <v>1137761000</v>
       </c>
       <c r="F5" t="n">
-        <v>1262723000</v>
+        <v>1170801000</v>
       </c>
       <c r="G5" t="n">
-        <v>29564000</v>
+        <v>-1008984000</v>
       </c>
       <c r="H5" t="n">
-        <v>1288529000</v>
+        <v>159482000</v>
       </c>
       <c r="I5" t="n">
-        <v>-958412000</v>
+        <v>-1004115000</v>
       </c>
       <c r="J5" t="n">
-        <v>29564000</v>
+        <v>-1008984000</v>
       </c>
       <c r="K5" t="n">
-        <v>3758000</v>
+        <v>2335000</v>
       </c>
       <c r="L5" t="n">
-        <v>29564000</v>
+        <v>-1008984000</v>
       </c>
       <c r="M5" t="n">
-        <v>726780000</v>
+        <v>-576888000</v>
       </c>
       <c r="N5" t="n">
-        <v>88709000</v>
+        <v>-1009144000</v>
       </c>
       <c r="O5" t="n">
-        <v>59145000</v>
+        <v>-160000</v>
       </c>
       <c r="P5" t="n">
-        <v>29564000</v>
+        <v>-1008984000</v>
       </c>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
+      <c r="R5" t="n">
+        <v>-1757869000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>513550000</v>
+      </c>
       <c r="T5" t="n">
-        <v>160371000</v>
+        <v>135155000</v>
       </c>
       <c r="U5" t="n">
-        <v>160371000</v>
+        <v>135155000</v>
       </c>
       <c r="V5" t="n">
-        <v>1982644000</v>
+        <v>1487244000</v>
       </c>
       <c r="W5" t="n">
-        <v>698699000</v>
+        <v>432897000</v>
       </c>
       <c r="X5" t="n">
-        <v>698699000</v>
+        <v>432897000</v>
       </c>
       <c r="Y5" t="n">
-        <v>1483000</v>
+        <v>801000</v>
       </c>
       <c r="Z5" t="n">
-        <v>697216000</v>
+        <v>432096000</v>
       </c>
       <c r="AA5" t="n">
-        <v>1283945000</v>
+        <v>1054347000</v>
       </c>
       <c r="AB5" t="n">
-        <v>564024000</v>
+        <v>737904000</v>
       </c>
       <c r="AC5" t="n">
-        <v>2275000</v>
+        <v>1534000</v>
       </c>
       <c r="AD5" t="n">
-        <v>561749000</v>
+        <v>736370000</v>
       </c>
       <c r="AE5" t="n">
-        <v>71082000</v>
+        <v>24686000</v>
       </c>
       <c r="AF5" t="n">
-        <v>570758000</v>
+        <v>276230000</v>
       </c>
       <c r="AG5" t="n">
-        <v>517803000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>878000</v>
-      </c>
+        <v>233686000</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
-        <v>52077000</v>
+        <v>42544000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2071353000</v>
+        <v>478100000</v>
       </c>
       <c r="AK5" t="n">
-        <v>1745820000</v>
-      </c>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="n">
-        <v>10108000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>10108000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>10108000</v>
-      </c>
+        <v>427868000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>342000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>342000</v>
+      </c>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="n">
         <v>0</v>
       </c>
@@ -2367,76 +2369,74 @@
         <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>1735712000</v>
+        <v>427526000</v>
       </c>
       <c r="AT5" t="n">
-        <v>-902045000</v>
+        <v>-1107687000</v>
       </c>
       <c r="AU5" t="n">
-        <v>2637757000</v>
+        <v>1535213000</v>
       </c>
       <c r="AV5" t="n">
-        <v>487965000</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>162393000</v>
-      </c>
+        <v>9102000</v>
+      </c>
+      <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="n">
-        <v>1120552000</v>
+        <v>935693000</v>
       </c>
       <c r="AY5" t="n">
-        <v>590093000</v>
+        <v>393007000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>276754000</v>
+        <v>197411000</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>325533000</v>
+        <v>50232000</v>
       </c>
       <c r="BC5" t="n">
-        <v>112343000</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>45288000</v>
+        <v>4249000</v>
       </c>
       <c r="BE5" t="n">
-        <v>5735000</v>
+        <v>10672000</v>
       </c>
       <c r="BF5" t="n">
-        <v>-3704000</v>
+        <v>-1218000</v>
       </c>
       <c r="BG5" t="n">
-        <v>1112000</v>
+        <v>7180000</v>
       </c>
       <c r="BH5" t="n">
-        <v>8327000</v>
+        <v>4710000</v>
       </c>
       <c r="BI5" t="n">
-        <v>91808000</v>
+        <v>3704000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>23020000</v>
+        <v>848000</v>
       </c>
       <c r="BK5" t="n">
-        <v>-19353000</v>
+        <v>-7224000</v>
       </c>
       <c r="BL5" t="n">
-        <v>42373000</v>
+        <v>8072000</v>
       </c>
       <c r="BM5" t="n">
-        <v>47339000</v>
+        <v>30759000</v>
       </c>
       <c r="BN5" t="n">
-        <v>564000</v>
+        <v>54000</v>
       </c>
       <c r="BO5" t="n">
-        <v>46775000</v>
+        <v>30705000</v>
       </c>
       <c r="BP5" t="n">
-        <v>46775000</v>
+        <v>30705000</v>
       </c>
     </row>
   </sheetData>
@@ -2687,554 +2687,554 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>-8018000</v>
+        <v>-79727000</v>
       </c>
       <c r="C2" t="n">
-        <v>-35689000</v>
+        <v>-30490000</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>106000000</v>
       </c>
       <c r="E2" t="n">
-        <v>58000000</v>
+        <v>53459000</v>
       </c>
       <c r="F2" t="n">
-        <v>-2772000</v>
+        <v>-18767000</v>
       </c>
       <c r="G2" t="n">
-        <v>30705000</v>
+        <v>46775000</v>
       </c>
       <c r="H2" t="n">
-        <v>2898000</v>
+        <v>8143000</v>
       </c>
       <c r="I2" t="n">
-        <v>-24000</v>
+        <v>235000</v>
       </c>
       <c r="J2" t="n">
-        <v>27831000</v>
+        <v>38397000</v>
       </c>
       <c r="K2" t="n">
-        <v>32435000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>10800000</v>
-      </c>
+        <v>126994000</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>58000000</v>
+        <v>53459000</v>
       </c>
       <c r="N2" t="n">
-        <v>58000000</v>
+        <v>53459000</v>
       </c>
       <c r="O2" t="n">
-        <v>-35689000</v>
+        <v>75510000</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-16193000</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
+        <v>-16193000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
       <c r="S2" t="n">
-        <v>-35689000</v>
+        <v>91703000</v>
       </c>
       <c r="T2" t="n">
-        <v>-35689000</v>
+        <v>-14297000</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>106000000</v>
       </c>
       <c r="V2" t="n">
-        <v>642000</v>
+        <v>-27637000</v>
       </c>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-8870000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>-8870000</v>
       </c>
       <c r="AA2" t="n">
-        <v>642000</v>
+        <v>-18767000</v>
       </c>
       <c r="AB2" t="n">
-        <v>3414000</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>-2772000</v>
+        <v>-18767000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-5246000</v>
+        <v>-60960000</v>
       </c>
       <c r="AE2" t="n">
-        <v>2000</v>
+        <v>951000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-5008000</v>
+        <v>-22208000</v>
       </c>
       <c r="AG2" t="n">
-        <v>58404000</v>
+        <v>58568000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>-2874000</v>
       </c>
       <c r="AI2" t="n">
-        <v>37425000</v>
+        <v>155309000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>30168000</v>
+        <v>-108648000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-6443000</v>
+        <v>2021000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-2746000</v>
+        <v>12760000</v>
       </c>
       <c r="AM2" t="n">
-        <v>108858000</v>
-      </c>
-      <c r="AN2" t="inlineStr"/>
+        <v>125170000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>19505000</v>
+      </c>
       <c r="AO2" t="n">
-        <v>7265000</v>
+        <v>5880000</v>
       </c>
       <c r="AP2" t="n">
-        <v>38531000</v>
+        <v>81618000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>38531000</v>
+        <v>81618000</v>
       </c>
       <c r="AR2" t="n">
-        <v>1771000</v>
+        <v>2988000</v>
       </c>
       <c r="AS2" t="n">
-        <v>-87779000</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>4394000</v>
       </c>
       <c r="AU2" t="n">
-        <v>-170219000</v>
+        <v>-458696000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
-        <v>-18961000</v>
+        <v>-69366000</v>
       </c>
       <c r="C3" t="n">
-        <v>-92856000</v>
+        <v>-238390000</v>
       </c>
       <c r="D3" t="n">
-        <v>28560000</v>
+        <v>119380000</v>
       </c>
       <c r="E3" t="n">
-        <v>75364000</v>
+        <v>147373000</v>
       </c>
       <c r="F3" t="n">
-        <v>-8010000</v>
+        <v>-43227000</v>
       </c>
       <c r="G3" t="n">
-        <v>2898000</v>
+        <v>12874000</v>
       </c>
       <c r="H3" t="n">
-        <v>12874000</v>
+        <v>46775000</v>
       </c>
       <c r="I3" t="n">
-        <v>-187000</v>
+        <v>302000</v>
       </c>
       <c r="J3" t="n">
-        <v>-9789000</v>
+        <v>-34203000</v>
       </c>
       <c r="K3" t="n">
-        <v>9585000</v>
+        <v>26088000</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>75364000</v>
+        <v>147373000</v>
       </c>
       <c r="N3" t="n">
-        <v>75364000</v>
+        <v>147373000</v>
       </c>
       <c r="O3" t="n">
-        <v>-64296000</v>
+        <v>-119010000</v>
       </c>
       <c r="P3" t="n">
-        <v>-1259000</v>
+        <v>53921000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1259000</v>
+        <v>-65459000</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>119380000</v>
       </c>
       <c r="S3" t="n">
-        <v>-63037000</v>
+        <v>-172931000</v>
       </c>
       <c r="T3" t="n">
-        <v>-91597000</v>
+        <v>-172931000</v>
       </c>
       <c r="U3" t="n">
-        <v>28560000</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>-8423000</v>
+        <v>-34152000</v>
       </c>
       <c r="W3" t="n">
-        <v>1354000</v>
+        <v>5276000</v>
       </c>
       <c r="X3" t="n">
-        <v>-1767000</v>
+        <v>3799000</v>
       </c>
       <c r="Y3" t="n">
-        <v>7000</v>
+        <v>3800000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-1774000</v>
+        <v>-1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-8010000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
+        <v>-43227000</v>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
-        <v>-8010000</v>
+        <v>-43227000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-10951000</v>
+        <v>-26139000</v>
       </c>
       <c r="AE3" t="n">
-        <v>4000</v>
+        <v>65000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-11738000</v>
+        <v>-16142000</v>
       </c>
       <c r="AG3" t="n">
-        <v>52831000</v>
+        <v>137639000</v>
       </c>
       <c r="AH3" t="n">
-        <v>1808000</v>
+        <v>549000</v>
       </c>
       <c r="AI3" t="n">
-        <v>22452000</v>
+        <v>121305000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>14991000</v>
+        <v>40053000</v>
       </c>
       <c r="AK3" t="n">
-        <v>11973000</v>
+        <v>-13406000</v>
       </c>
       <c r="AL3" t="n">
-        <v>1607000</v>
+        <v>-10862000</v>
       </c>
       <c r="AM3" t="n">
-        <v>115496000</v>
-      </c>
-      <c r="AN3" t="inlineStr"/>
+        <v>154554000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0</v>
+      </c>
       <c r="AO3" t="n">
-        <v>-818000</v>
+        <v>3311000</v>
       </c>
       <c r="AP3" t="n">
-        <v>63340000</v>
+        <v>82430000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>63340000</v>
+        <v>82430000</v>
       </c>
       <c r="AR3" t="n">
-        <v>-151000</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
+        <v>-1956000</v>
+      </c>
+      <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
-        <v>-404680000</v>
+        <v>-14020000</v>
       </c>
       <c r="AU3" t="n">
-        <v>-195242000</v>
+        <v>-1073821000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
-        <v>-69366000</v>
+        <v>-18961000</v>
       </c>
       <c r="C4" t="n">
-        <v>-238390000</v>
+        <v>-92856000</v>
       </c>
       <c r="D4" t="n">
-        <v>119380000</v>
+        <v>28560000</v>
       </c>
       <c r="E4" t="n">
-        <v>147373000</v>
+        <v>75364000</v>
       </c>
       <c r="F4" t="n">
-        <v>-43227000</v>
+        <v>-8010000</v>
       </c>
       <c r="G4" t="n">
+        <v>2898000</v>
+      </c>
+      <c r="H4" t="n">
         <v>12874000</v>
       </c>
-      <c r="H4" t="n">
-        <v>46775000</v>
-      </c>
       <c r="I4" t="n">
-        <v>302000</v>
+        <v>-187000</v>
       </c>
       <c r="J4" t="n">
-        <v>-34203000</v>
+        <v>-9789000</v>
       </c>
       <c r="K4" t="n">
-        <v>26088000</v>
+        <v>9585000</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>147373000</v>
+        <v>75364000</v>
       </c>
       <c r="N4" t="n">
-        <v>147373000</v>
+        <v>75364000</v>
       </c>
       <c r="O4" t="n">
-        <v>-119010000</v>
+        <v>-64296000</v>
       </c>
       <c r="P4" t="n">
-        <v>53921000</v>
+        <v>-1259000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-65459000</v>
+        <v>-1259000</v>
       </c>
       <c r="R4" t="n">
-        <v>119380000</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-172931000</v>
+        <v>-63037000</v>
       </c>
       <c r="T4" t="n">
-        <v>-172931000</v>
+        <v>-91597000</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>28560000</v>
       </c>
       <c r="V4" t="n">
-        <v>-34152000</v>
+        <v>-8423000</v>
       </c>
       <c r="W4" t="n">
-        <v>5276000</v>
+        <v>1354000</v>
       </c>
       <c r="X4" t="n">
-        <v>3799000</v>
+        <v>-1767000</v>
       </c>
       <c r="Y4" t="n">
-        <v>3800000</v>
+        <v>7000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-1000</v>
+        <v>-1774000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-43227000</v>
-      </c>
-      <c r="AB4" t="inlineStr"/>
+        <v>-8010000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
       <c r="AC4" t="n">
-        <v>-43227000</v>
+        <v>-8010000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-26139000</v>
+        <v>-10951000</v>
       </c>
       <c r="AE4" t="n">
-        <v>65000</v>
+        <v>4000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-16142000</v>
+        <v>-11738000</v>
       </c>
       <c r="AG4" t="n">
-        <v>137639000</v>
+        <v>52831000</v>
       </c>
       <c r="AH4" t="n">
-        <v>549000</v>
+        <v>1808000</v>
       </c>
       <c r="AI4" t="n">
-        <v>121305000</v>
+        <v>22452000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>40053000</v>
+        <v>14991000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-13406000</v>
+        <v>11973000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-10862000</v>
+        <v>1607000</v>
       </c>
       <c r="AM4" t="n">
-        <v>154554000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0</v>
-      </c>
+        <v>115496000</v>
+      </c>
+      <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>3311000</v>
+        <v>-818000</v>
       </c>
       <c r="AP4" t="n">
-        <v>82430000</v>
+        <v>63340000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>82430000</v>
+        <v>63340000</v>
       </c>
       <c r="AR4" t="n">
-        <v>-1956000</v>
-      </c>
-      <c r="AS4" t="inlineStr"/>
+        <v>-151000</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
       <c r="AT4" t="n">
-        <v>-14020000</v>
+        <v>-404680000</v>
       </c>
       <c r="AU4" t="n">
-        <v>-1073821000</v>
+        <v>-195242000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>-79727000</v>
+        <v>-8018000</v>
       </c>
       <c r="C5" t="n">
-        <v>-30490000</v>
+        <v>-35689000</v>
       </c>
       <c r="D5" t="n">
-        <v>106000000</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>53459000</v>
+        <v>58000000</v>
       </c>
       <c r="F5" t="n">
-        <v>-18767000</v>
+        <v>-2772000</v>
       </c>
       <c r="G5" t="n">
-        <v>46775000</v>
+        <v>30705000</v>
       </c>
       <c r="H5" t="n">
-        <v>8143000</v>
+        <v>2898000</v>
       </c>
       <c r="I5" t="n">
-        <v>235000</v>
+        <v>-24000</v>
       </c>
       <c r="J5" t="n">
-        <v>38397000</v>
+        <v>27831000</v>
       </c>
       <c r="K5" t="n">
-        <v>126994000</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
+        <v>32435000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>10800000</v>
+      </c>
       <c r="M5" t="n">
-        <v>53459000</v>
+        <v>58000000</v>
       </c>
       <c r="N5" t="n">
-        <v>53459000</v>
+        <v>58000000</v>
       </c>
       <c r="O5" t="n">
-        <v>75510000</v>
+        <v>-35689000</v>
       </c>
       <c r="P5" t="n">
-        <v>-16193000</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-16193000</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>91703000</v>
+        <v>-35689000</v>
       </c>
       <c r="T5" t="n">
-        <v>-14297000</v>
+        <v>-35689000</v>
       </c>
       <c r="U5" t="n">
-        <v>106000000</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>-27637000</v>
+        <v>642000</v>
       </c>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>-8870000</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>-8870000</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>-18767000</v>
+        <v>642000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>3414000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-18767000</v>
+        <v>-2772000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-60960000</v>
+        <v>-5246000</v>
       </c>
       <c r="AE5" t="n">
-        <v>951000</v>
+        <v>2000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-22208000</v>
+        <v>-5008000</v>
       </c>
       <c r="AG5" t="n">
-        <v>58568000</v>
+        <v>58404000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-2874000</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>155309000</v>
+        <v>37425000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-108648000</v>
+        <v>30168000</v>
       </c>
       <c r="AK5" t="n">
-        <v>2021000</v>
+        <v>-6443000</v>
       </c>
       <c r="AL5" t="n">
-        <v>12760000</v>
+        <v>-2746000</v>
       </c>
       <c r="AM5" t="n">
-        <v>125170000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>19505000</v>
-      </c>
+        <v>108858000</v>
+      </c>
+      <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>5880000</v>
+        <v>7265000</v>
       </c>
       <c r="AP5" t="n">
-        <v>81618000</v>
+        <v>38531000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>81618000</v>
+        <v>38531000</v>
       </c>
       <c r="AR5" t="n">
-        <v>2988000</v>
+        <v>1771000</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>-87779000</v>
       </c>
       <c r="AT5" t="n">
-        <v>4394000</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>-458696000</v>
+        <v>-170219000</v>
       </c>
     </row>
   </sheetData>
@@ -3769,197 +3769,197 @@
       </c>
       <c r="CZ1" t="inlineStr">
         <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="EC1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="EE1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>priceToBook</t>
         </is>
       </c>
-      <c r="EF1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="EG1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="EH1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>prevName</t>
         </is>
       </c>
-      <c r="EI1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>nameChangeDate</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
         </is>
       </c>
       <c r="EM1" t="inlineStr">
@@ -4092,7 +4092,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.594</v>
+        <v>0.608</v>
       </c>
       <c r="AF2" t="n">
         <v>0.0013711152</v>
@@ -4222,7 +4222,7 @@
         <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BV2" t="n">
         <v>17.008648</v>
@@ -4334,148 +4334,148 @@
           <t>C ZENITH CHEM</t>
         </is>
       </c>
-      <c r="CZ2" t="b">
-        <v>0</v>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
       </c>
       <c r="DA2" t="n">
+        <v>-25</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DD2" t="n">
+        <v>1742178493</v>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>finmb_9408527</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DI2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DK2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>China Zenith Chemical Group Limited</t>
+        </is>
+      </c>
+      <c r="DM2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DN2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DO2" t="n">
         <v>1039743000000</v>
       </c>
-      <c r="DB2" t="n">
+      <c r="DP2" t="n">
         <v>-0.005</v>
       </c>
-      <c r="DC2" t="inlineStr">
+      <c r="DQ2" t="inlineStr">
         <is>
           <t>0.015 - 0.02</t>
         </is>
       </c>
-      <c r="DD2" t="inlineStr">
+      <c r="DR2" t="inlineStr">
         <is>
           <t>HKSE</t>
         </is>
       </c>
-      <c r="DE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH2" t="inlineStr">
+      <c r="DS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV2" t="inlineStr">
         <is>
           <t>0.015 - 0.02</t>
         </is>
       </c>
-      <c r="DI2" t="n">
+      <c r="DW2" t="n">
         <v>-0.005</v>
       </c>
-      <c r="DJ2" t="n">
+      <c r="DX2" t="n">
         <v>-0.25</v>
       </c>
-      <c r="DK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DL2" t="n">
+      <c r="DY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ2" t="n">
         <v>1740740340</v>
       </c>
-      <c r="DM2" t="n">
+      <c r="EA2" t="n">
         <v>1740740340</v>
       </c>
-      <c r="DN2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DO2" t="n">
+      <c r="EB2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EC2" t="n">
         <v>10.94</v>
       </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>China Zenith Chemical Group Limited</t>
-        </is>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DR2" t="n">
-        <v>1742178493</v>
-      </c>
-      <c r="DS2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>finmb_9408527</t>
-        </is>
-      </c>
-      <c r="DU2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="DW2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DX2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="DY2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DZ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>0</v>
-      </c>
       <c r="ED2" t="n">
         <v>0</v>
       </c>
       <c r="EE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH2" t="n">
         <v>-0.01884422</v>
       </c>
-      <c r="EF2" t="n">
+      <c r="EI2" t="n">
         <v>15</v>
       </c>
-      <c r="EG2" t="n">
+      <c r="EJ2" t="n">
         <v>15</v>
       </c>
-      <c r="EH2" t="inlineStr">
+      <c r="EK2" t="inlineStr">
         <is>
           <t>Xinyang Maojian Group Limited</t>
         </is>
       </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="EK2" t="n">
-        <v>-25</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>0.015</v>
+      <c r="EL2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
       </c>
       <c r="EM2" t="inlineStr"/>
     </row>
